--- a/Optimal parameters database/BL_parameter_database.xlsx
+++ b/Optimal parameters database/BL_parameter_database.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -13,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="63" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="189" uniqueCount="17">
   <si>
     <t>airfoil_id</t>
   </si>
@@ -117,10 +118,10 @@
     <col min="3" max="3" width="6.7109375" customWidth="true"/>
     <col min="4" max="4" width="8.140625" customWidth="true"/>
     <col min="5" max="5" width="5" customWidth="true"/>
-    <col min="6" max="6" width="13.7109375" customWidth="true"/>
+    <col min="6" max="6" width="14.7109375" customWidth="true"/>
     <col min="7" max="7" width="14.7109375" customWidth="true"/>
     <col min="8" max="8" width="13.7109375" customWidth="true"/>
-    <col min="9" max="9" width="12.7109375" customWidth="true"/>
+    <col min="9" max="9" width="14.7109375" customWidth="true"/>
     <col min="10" max="10" width="12.7109375" customWidth="true"/>
     <col min="11" max="11" width="12.7109375" customWidth="true"/>
     <col min="12" max="12" width="12.7109375" customWidth="true"/>
@@ -193,31 +194,31 @@
         <v>0.59999999999999998</v>
       </c>
       <c r="F2" s="0">
-        <v>0.17779716846897992</v>
+        <v>0.25072346268270418</v>
       </c>
       <c r="G2" s="0">
-        <v>0.25018284236155042</v>
+        <v>0.54818544755266052</v>
       </c>
       <c r="H2" s="0">
-        <v>0.52305320840203062</v>
+        <v>0.59437168095165349</v>
       </c>
       <c r="I2" s="0">
-        <v>0.77318347911645169</v>
+        <v>0.74835084905465976</v>
       </c>
       <c r="J2" s="0">
-        <v>4.6320965847155193</v>
+        <v>4.052926349247115</v>
       </c>
       <c r="K2" s="0">
-        <v>0.48654341615297614</v>
+        <v>3.2456963678207069</v>
       </c>
       <c r="L2" s="0">
-        <v>5.6692398346984287</v>
+        <v>6.5304651891613874</v>
       </c>
       <c r="M2" s="0">
-        <v>4.4384763653385315</v>
+        <v>2.3560581780727015</v>
       </c>
       <c r="N2" s="0">
-        <v>0.85098771502300885</v>
+        <v>0.85066825656879552</v>
       </c>
       <c r="O2" s="0" t="s">
         <v>16</v>
@@ -240,31 +241,31 @@
         <v>1.2</v>
       </c>
       <c r="F3" s="0">
-        <v>0.086538387043415904</v>
+        <v>0.36735561827643698</v>
       </c>
       <c r="G3" s="0">
-        <v>0.0035381930091205049</v>
+        <v>0.42012672388406991</v>
       </c>
       <c r="H3" s="0">
-        <v>0.48746587967414917</v>
+        <v>0.022395136814943317</v>
       </c>
       <c r="I3" s="0">
-        <v>0.68889018948759628</v>
+        <v>0.17170769534068964</v>
       </c>
       <c r="J3" s="0">
-        <v>2.4752238559352913</v>
+        <v>3.3328782073942911</v>
       </c>
       <c r="K3" s="0">
-        <v>4.249698029431304</v>
+        <v>4.9999991815405913</v>
       </c>
       <c r="L3" s="0">
-        <v>11.758325273796331</v>
+        <v>7.1597568739365158</v>
       </c>
       <c r="M3" s="0">
-        <v>4.9994146892468994</v>
+        <v>3.3598492023477298</v>
       </c>
       <c r="N3" s="0">
-        <v>0.85505678811240804</v>
+        <v>0.8502732760359607</v>
       </c>
       <c r="O3" s="0" t="s">
         <v>16</v>
@@ -287,31 +288,31 @@
         <v>1.8</v>
       </c>
       <c r="F4" s="0">
-        <v>0.18506279975974727</v>
+        <v>0.017630693414357357</v>
       </c>
       <c r="G4" s="0">
-        <v>0.22787686995160286</v>
+        <v>0.79930930677250967</v>
       </c>
       <c r="H4" s="0">
-        <v>0.28583466406602265</v>
+        <v>0.16554741308109522</v>
       </c>
       <c r="I4" s="0">
-        <v>0.74518083533905877</v>
+        <v>0.0011107045618913959</v>
       </c>
       <c r="J4" s="0">
-        <v>9.3182685313909897</v>
+        <v>5.8539792222542353</v>
       </c>
       <c r="K4" s="0">
-        <v>2.9441862925070241</v>
+        <v>4.9992924310937585</v>
       </c>
       <c r="L4" s="0">
-        <v>14.510745939189931</v>
+        <v>14.969895012220791</v>
       </c>
       <c r="M4" s="0">
-        <v>4.8653344539104211</v>
+        <v>4.6873584841916447</v>
       </c>
       <c r="N4" s="0">
-        <v>0.94966839441095607</v>
+        <v>0.9499861373485462</v>
       </c>
       <c r="O4" s="0" t="s">
         <v>16</v>
@@ -334,31 +335,31 @@
         <v>2.3999999999999999</v>
       </c>
       <c r="F5" s="0">
-        <v>0.084862124989020071</v>
+        <v>0.053842952413495217</v>
       </c>
       <c r="G5" s="0">
-        <v>0.69088782314164576</v>
+        <v>0.79984764401395614</v>
       </c>
       <c r="H5" s="0">
-        <v>0.30002803397335037</v>
+        <v>0.44721584767023004</v>
       </c>
       <c r="I5" s="0">
-        <v>0.59646072380432991</v>
+        <v>0.79999809129034505</v>
       </c>
       <c r="J5" s="0">
-        <v>7.7349554523551465</v>
+        <v>9.9999987133849739</v>
       </c>
       <c r="K5" s="0">
-        <v>4.9999991295096251</v>
+        <v>4.9994065558843905</v>
       </c>
       <c r="L5" s="0">
-        <v>4.8554457385266634</v>
+        <v>6.6653982500237961</v>
       </c>
       <c r="M5" s="0">
-        <v>4.999986946802772</v>
+        <v>4.9999975641364607</v>
       </c>
       <c r="N5" s="0">
-        <v>0.9499991030216951</v>
+        <v>0.9498081406338178</v>
       </c>
       <c r="O5" s="0" t="s">
         <v>16</v>
@@ -381,31 +382,31 @@
         <v>0.59999999999999998</v>
       </c>
       <c r="F6" s="0">
-        <v>0.40544947214190497</v>
+        <v>0.33945101622453233</v>
       </c>
       <c r="G6" s="0">
-        <v>0.46806797175702092</v>
+        <v>0.45365703129819518</v>
       </c>
       <c r="H6" s="0">
-        <v>0.027553467374409293</v>
+        <v>0.1125675003693984</v>
       </c>
       <c r="I6" s="0">
-        <v>0.40898108222334917</v>
+        <v>0.61751305751202856</v>
       </c>
       <c r="J6" s="0">
-        <v>2.1942507518939576</v>
+        <v>3.9776079061566909</v>
       </c>
       <c r="K6" s="0">
-        <v>3.9087794629456125</v>
+        <v>1.5381819716701286</v>
       </c>
       <c r="L6" s="0">
-        <v>1.5880994628084091</v>
+        <v>12.325474363444778</v>
       </c>
       <c r="M6" s="0">
-        <v>1.8686378479202079</v>
+        <v>0.18016933687333625</v>
       </c>
       <c r="N6" s="0">
-        <v>0.85021069656876236</v>
+        <v>0.85025002465646049</v>
       </c>
       <c r="O6" s="0" t="s">
         <v>16</v>
@@ -428,31 +429,31 @@
         <v>1.2</v>
       </c>
       <c r="F7" s="0">
-        <v>0.079595058477246683</v>
+        <v>0.22915114127635425</v>
       </c>
       <c r="G7" s="0">
-        <v>0.47200271733991217</v>
+        <v>0.17034545699161718</v>
       </c>
       <c r="H7" s="0">
-        <v>0.20639578065874611</v>
+        <v>0.15125556559640024</v>
       </c>
       <c r="I7" s="0">
-        <v>0.12899040717213694</v>
+        <v>0.73773781618125867</v>
       </c>
       <c r="J7" s="0">
-        <v>2.6669578050133298</v>
+        <v>7.5210746877136225</v>
       </c>
       <c r="K7" s="0">
-        <v>2.3904315779541441</v>
+        <v>0.27596880009706504</v>
       </c>
       <c r="L7" s="0">
-        <v>9.1031545538340861</v>
+        <v>3.1850965761072985</v>
       </c>
       <c r="M7" s="0">
-        <v>4.9999930305918241</v>
+        <v>0.31424149874642671</v>
       </c>
       <c r="N7" s="0">
-        <v>0.85118895269782036</v>
+        <v>0.94999933338847831</v>
       </c>
       <c r="O7" s="0" t="s">
         <v>16</v>
@@ -475,31 +476,31 @@
         <v>1.8</v>
       </c>
       <c r="F8" s="0">
-        <v>0.15849959306378159</v>
+        <v>0.23234615749534557</v>
       </c>
       <c r="G8" s="0">
-        <v>0.129692941124679</v>
+        <v>0.50818802048500999</v>
       </c>
       <c r="H8" s="0">
-        <v>0.28745188958908002</v>
+        <v>0.16146972625558131</v>
       </c>
       <c r="I8" s="0">
-        <v>0.62016176574305382</v>
+        <v>0.18319416133565555</v>
       </c>
       <c r="J8" s="0">
-        <v>4.4100755762093442</v>
+        <v>4.53129423041519</v>
       </c>
       <c r="K8" s="0">
-        <v>4.9992068998187698</v>
+        <v>4.999999946248364</v>
       </c>
       <c r="L8" s="0">
-        <v>6.1472383748651573</v>
+        <v>7.706407671696029</v>
       </c>
       <c r="M8" s="0">
-        <v>1.6181451154869975</v>
+        <v>0.7135196167830411</v>
       </c>
       <c r="N8" s="0">
-        <v>0.94942496336555526</v>
+        <v>0.85000071512553588</v>
       </c>
       <c r="O8" s="0" t="s">
         <v>16</v>
@@ -522,31 +523,31 @@
         <v>2.3999999999999999</v>
       </c>
       <c r="F9" s="0">
-        <v>0.40140932557482678</v>
+        <v>0.075296744116422787</v>
       </c>
       <c r="G9" s="0">
-        <v>0.35123779738167632</v>
+        <v>0.18230977525979675</v>
       </c>
       <c r="H9" s="0">
-        <v>0.06429433155758027</v>
+        <v>0.28889692101203795</v>
       </c>
       <c r="I9" s="0">
-        <v>0.088194141999536679</v>
+        <v>0.44991298002403451</v>
       </c>
       <c r="J9" s="0">
-        <v>5.7340093364658245</v>
+        <v>4.5218903479303672</v>
       </c>
       <c r="K9" s="0">
-        <v>3.2120556126541278</v>
+        <v>4.9999927204477048</v>
       </c>
       <c r="L9" s="0">
-        <v>10.377492290031139</v>
+        <v>7.3335879931846257</v>
       </c>
       <c r="M9" s="0">
-        <v>4.6081932771636325</v>
+        <v>4.3727290064539783</v>
       </c>
       <c r="N9" s="0">
-        <v>0.91024793307739627</v>
+        <v>0.85029474969581465</v>
       </c>
       <c r="O9" s="0" t="s">
         <v>16</v>
@@ -569,31 +570,31 @@
         <v>0.59999999999999998</v>
       </c>
       <c r="F10" s="0">
-        <v>0.070089685683317082</v>
+        <v>0.15280168014918846</v>
       </c>
       <c r="G10" s="0">
-        <v>0.79835174486827176</v>
+        <v>0.79987982259807589</v>
       </c>
       <c r="H10" s="0">
-        <v>0.65856568505645818</v>
+        <v>0.57911643197040608</v>
       </c>
       <c r="I10" s="0">
-        <v>0.79879177683959579</v>
+        <v>0.7999709732951571</v>
       </c>
       <c r="J10" s="0">
-        <v>0.87993287991742153</v>
+        <v>0.57993459365353717</v>
       </c>
       <c r="K10" s="0">
-        <v>4.6518802794880472</v>
+        <v>4.9999990994997878</v>
       </c>
       <c r="L10" s="0">
-        <v>5.0177492310628162</v>
+        <v>1.8351409564518728</v>
       </c>
       <c r="M10" s="0">
-        <v>0.47936646561663809</v>
+        <v>1.6733124605806158</v>
       </c>
       <c r="N10" s="0">
-        <v>0.94999485448706489</v>
+        <v>0.94989435695721725</v>
       </c>
       <c r="O10" s="0" t="s">
         <v>16</v>
@@ -616,31 +617,31 @@
         <v>1.2</v>
       </c>
       <c r="F11" s="0">
-        <v>0.16184045799977068</v>
+        <v>0.25214816041529914</v>
       </c>
       <c r="G11" s="0">
-        <v>0.5737240844817183</v>
+        <v>0.7998895481876549</v>
       </c>
       <c r="H11" s="0">
-        <v>0.15412856109930334</v>
+        <v>0.10439739735539764</v>
       </c>
       <c r="I11" s="0">
-        <v>0.23205880693906522</v>
+        <v>0.029894450489093494</v>
       </c>
       <c r="J11" s="0">
-        <v>2.8718227579814819</v>
+        <v>2.6593051328946817</v>
       </c>
       <c r="K11" s="0">
-        <v>3.7332531290136841</v>
+        <v>4.603172102825468</v>
       </c>
       <c r="L11" s="0">
-        <v>0.29093152828861146</v>
+        <v>1.4539026003333917</v>
       </c>
       <c r="M11" s="0">
-        <v>0.29604913406790512</v>
+        <v>0.13757618733489851</v>
       </c>
       <c r="N11" s="0">
-        <v>0.94999953070817234</v>
+        <v>0.94999826734614579</v>
       </c>
       <c r="O11" s="0" t="s">
         <v>16</v>
@@ -663,31 +664,31 @@
         <v>1.8</v>
       </c>
       <c r="F12" s="0">
-        <v>0.4873424836305783</v>
+        <v>0.38535877127083035</v>
       </c>
       <c r="G12" s="0">
-        <v>0.71934456632013055</v>
+        <v>0.3475320202746266</v>
       </c>
       <c r="H12" s="0">
-        <v>0.18634471523981519</v>
+        <v>0.044594147995656378</v>
       </c>
       <c r="I12" s="0">
-        <v>0.54502566328023761</v>
+        <v>0.42328807178221373</v>
       </c>
       <c r="J12" s="0">
-        <v>1.9173466481882893</v>
+        <v>2.7309958543693949</v>
       </c>
       <c r="K12" s="0">
-        <v>4.999999993154626</v>
+        <v>4.9998805785451932</v>
       </c>
       <c r="L12" s="0">
-        <v>0.53141962111554975</v>
+        <v>0.78213924517372968</v>
       </c>
       <c r="M12" s="0">
-        <v>1.9258780138083904</v>
+        <v>0.0012023331187529518</v>
       </c>
       <c r="N12" s="0">
-        <v>0.85000604162860427</v>
+        <v>0.85098748178759076</v>
       </c>
       <c r="O12" s="0" t="s">
         <v>16</v>
@@ -710,31 +711,31 @@
         <v>2.3999999999999999</v>
       </c>
       <c r="F13" s="0">
-        <v>0.11286619590591203</v>
+        <v>0.57818371188197226</v>
       </c>
       <c r="G13" s="0">
-        <v>0.058719539908619472</v>
+        <v>0.61870752448324506</v>
       </c>
       <c r="H13" s="0">
-        <v>0.54342595968161</v>
+        <v>0.084903209623124892</v>
       </c>
       <c r="I13" s="0">
-        <v>0.79998351858645789</v>
+        <v>0.0026865743989563208</v>
       </c>
       <c r="J13" s="0">
-        <v>7.1668197154796216</v>
+        <v>2.2977613572792439</v>
       </c>
       <c r="K13" s="0">
-        <v>0.92644085362783113</v>
+        <v>4.1583483072307699</v>
       </c>
       <c r="L13" s="0">
-        <v>7.6938166011480256</v>
+        <v>14.456496217744178</v>
       </c>
       <c r="M13" s="0">
-        <v>0.0021110778070803082</v>
+        <v>1.0279582423080076</v>
       </c>
       <c r="N13" s="0">
-        <v>0.94970504731388916</v>
+        <v>0.85244468150063835</v>
       </c>
       <c r="O13" s="0" t="s">
         <v>16</v>
@@ -757,31 +758,31 @@
         <v>0.59999999999999998</v>
       </c>
       <c r="F14" s="0">
-        <v>0.05164077053907068</v>
+        <v>0.018136486680792444</v>
       </c>
       <c r="G14" s="0">
-        <v>0.14994458302870128</v>
+        <v>0.068361907445573133</v>
       </c>
       <c r="H14" s="0">
-        <v>0.71197858605279962</v>
+        <v>0.5902023114166931</v>
       </c>
       <c r="I14" s="0">
-        <v>0.6761712988231382</v>
+        <v>0.44034464401044987</v>
       </c>
       <c r="J14" s="0">
-        <v>1.3953589987326396</v>
+        <v>1.8444732348040442</v>
       </c>
       <c r="K14" s="0">
-        <v>1.8874940062791437</v>
+        <v>2.1294285485083657</v>
       </c>
       <c r="L14" s="0">
-        <v>14.994081199721666</v>
+        <v>14.97032204659649</v>
       </c>
       <c r="M14" s="0">
-        <v>4.9999989857127263</v>
+        <v>4.4197233522943238</v>
       </c>
       <c r="N14" s="0">
-        <v>0.85026705401441027</v>
+        <v>0.8516137407529728</v>
       </c>
       <c r="O14" s="0" t="s">
         <v>16</v>
@@ -804,31 +805,31 @@
         <v>1.2</v>
       </c>
       <c r="F15" s="0">
-        <v>0.4335251633451665</v>
+        <v>0.25040187328285885</v>
       </c>
       <c r="G15" s="0">
-        <v>0.33909652635430992</v>
+        <v>0.18240110225094233</v>
       </c>
       <c r="H15" s="0">
-        <v>0.08528301317879726</v>
+        <v>0.32382791999444738</v>
       </c>
       <c r="I15" s="0">
-        <v>0.48620843614434145</v>
+        <v>0.72223058995439715</v>
       </c>
       <c r="J15" s="0">
-        <v>1.6153550157261203</v>
+        <v>4.1689755115445522</v>
       </c>
       <c r="K15" s="0">
-        <v>3.5771298953376913</v>
+        <v>4.5775689837632658</v>
       </c>
       <c r="L15" s="0">
-        <v>5.2594301538683093</v>
+        <v>12.299564047249108</v>
       </c>
       <c r="M15" s="0">
-        <v>4.9999933332245314</v>
+        <v>4.3478349962484071</v>
       </c>
       <c r="N15" s="0">
-        <v>0.85000238352840163</v>
+        <v>0.85698025004127754</v>
       </c>
       <c r="O15" s="0" t="s">
         <v>16</v>
@@ -851,31 +852,31 @@
         <v>1.8</v>
       </c>
       <c r="F16" s="0">
-        <v>0.05045317464999366</v>
+        <v>0.16780303342135056</v>
       </c>
       <c r="G16" s="0">
-        <v>0.15028276241720154</v>
+        <v>0.16437391314951305</v>
       </c>
       <c r="H16" s="0">
-        <v>0.39380210196046117</v>
+        <v>0.22983215481187164</v>
       </c>
       <c r="I16" s="0">
-        <v>0.37814379004385001</v>
+        <v>0.44389300378365526</v>
       </c>
       <c r="J16" s="0">
-        <v>4.3028015242069699</v>
+        <v>4.6716181989676224</v>
       </c>
       <c r="K16" s="0">
-        <v>2.8022066959843013</v>
+        <v>4.7651176912658748</v>
       </c>
       <c r="L16" s="0">
-        <v>9.0192655084473703</v>
+        <v>8.8629553832936701</v>
       </c>
       <c r="M16" s="0">
-        <v>4.9995995499064554</v>
+        <v>4.998995108896767</v>
       </c>
       <c r="N16" s="0">
-        <v>0.85070291403737308</v>
+        <v>0.85025439486400811</v>
       </c>
       <c r="O16" s="0" t="s">
         <v>16</v>
@@ -898,31 +899,31 @@
         <v>2.3999999999999999</v>
       </c>
       <c r="F17" s="0">
-        <v>0.12843511198511681</v>
+        <v>0.15475323760686424</v>
       </c>
       <c r="G17" s="0">
-        <v>0.010962434037761693</v>
+        <v>0.0061949364239365151</v>
       </c>
       <c r="H17" s="0">
-        <v>0.32338487619839018</v>
+        <v>0.32200709978645697</v>
       </c>
       <c r="I17" s="0">
-        <v>0.79982554906003678</v>
+        <v>0.79987570789354212</v>
       </c>
       <c r="J17" s="0">
-        <v>4.6445239961041782</v>
+        <v>3.8982204151908415</v>
       </c>
       <c r="K17" s="0">
-        <v>4.9694908018117392</v>
+        <v>4.9998686716936396</v>
       </c>
       <c r="L17" s="0">
-        <v>14.431534332414133</v>
+        <v>8.3726945135231912</v>
       </c>
       <c r="M17" s="0">
-        <v>4.9998202509743965</v>
+        <v>4.9997784565547825</v>
       </c>
       <c r="N17" s="0">
-        <v>0.85911826645353961</v>
+        <v>0.857684703797157</v>
       </c>
       <c r="O17" s="0" t="s">
         <v>16</v>
@@ -945,31 +946,31 @@
         <v>0.59999999999999998</v>
       </c>
       <c r="F18" s="0">
-        <v>0.65425821423141861</v>
+        <v>0.79620754825174389</v>
       </c>
       <c r="G18" s="0">
-        <v>0.79714004528762394</v>
+        <v>0.7663414832612564</v>
       </c>
       <c r="H18" s="0">
-        <v>0.62050955563580379</v>
+        <v>0.68124122588221891</v>
       </c>
       <c r="I18" s="0">
-        <v>0.79630826649901665</v>
+        <v>0.70778920691628378</v>
       </c>
       <c r="J18" s="0">
-        <v>2.7673106393600584</v>
+        <v>1.4083329738039883</v>
       </c>
       <c r="K18" s="0">
-        <v>0.46014034657149061</v>
+        <v>4.9997717648411708</v>
       </c>
       <c r="L18" s="0">
-        <v>14.998841132608105</v>
+        <v>0.24368060177999973</v>
       </c>
       <c r="M18" s="0">
-        <v>4.9981252695795968</v>
+        <v>4.9999889815421792</v>
       </c>
       <c r="N18" s="0">
-        <v>0.85008411545485319</v>
+        <v>0.85000485521882852</v>
       </c>
       <c r="O18" s="0" t="s">
         <v>16</v>
@@ -992,31 +993,31 @@
         <v>1.2</v>
       </c>
       <c r="F19" s="0">
-        <v>0.32285854523114427</v>
+        <v>0.79384304611236278</v>
       </c>
       <c r="G19" s="0">
-        <v>0.72025935188381685</v>
+        <v>0.5492884462002745</v>
       </c>
       <c r="H19" s="0">
-        <v>0.64075449364903792</v>
+        <v>0.4409287279364591</v>
       </c>
       <c r="I19" s="0">
-        <v>0.63357314788969843</v>
+        <v>0.5464000827737826</v>
       </c>
       <c r="J19" s="0">
-        <v>1.1508813535424467</v>
+        <v>4.2655361742581715</v>
       </c>
       <c r="K19" s="0">
-        <v>3.5940768866896464</v>
+        <v>0.8863045289133169</v>
       </c>
       <c r="L19" s="0">
-        <v>8.2139434357483267</v>
+        <v>10.146245101768555</v>
       </c>
       <c r="M19" s="0">
-        <v>4.9999999725394488</v>
+        <v>2.807021721840858</v>
       </c>
       <c r="N19" s="0">
-        <v>0.85000462031259949</v>
+        <v>0.85043904609234899</v>
       </c>
       <c r="O19" s="0" t="s">
         <v>16</v>
@@ -1039,31 +1040,31 @@
         <v>1.8</v>
       </c>
       <c r="F20" s="0">
-        <v>0.24079845460278487</v>
+        <v>0.26908200693442413</v>
       </c>
       <c r="G20" s="0">
-        <v>0.14395622778040629</v>
+        <v>0.53829113481929003</v>
       </c>
       <c r="H20" s="0">
-        <v>0.18527967304330445</v>
+        <v>0.29149968104969259</v>
       </c>
       <c r="I20" s="0">
-        <v>0.24074518952098922</v>
+        <v>0.15244916359584693</v>
       </c>
       <c r="J20" s="0">
-        <v>7.6399100065218093</v>
+        <v>3.3223908160910156</v>
       </c>
       <c r="K20" s="0">
-        <v>3.1543647480355181</v>
+        <v>4.9999974267700269</v>
       </c>
       <c r="L20" s="0">
-        <v>11.856564955942355</v>
+        <v>6.026449287201884</v>
       </c>
       <c r="M20" s="0">
-        <v>0.0058512144201197103</v>
+        <v>4.9999998393922791</v>
       </c>
       <c r="N20" s="0">
-        <v>0.85019145707951638</v>
+        <v>0.85016628535705496</v>
       </c>
       <c r="O20" s="0" t="s">
         <v>16</v>
@@ -1086,31 +1087,31 @@
         <v>2.3999999999999999</v>
       </c>
       <c r="F21" s="0">
-        <v>0.29067159882115851</v>
+        <v>0.32282472975149124</v>
       </c>
       <c r="G21" s="0">
-        <v>0.30806420151767644</v>
+        <v>0.18783361912760324</v>
       </c>
       <c r="H21" s="0">
-        <v>0.30504550480685594</v>
+        <v>0.09531340664071114</v>
       </c>
       <c r="I21" s="0">
-        <v>0.22690401108964223</v>
+        <v>0.54086851270335956</v>
       </c>
       <c r="J21" s="0">
-        <v>4.0268302263223106</v>
+        <v>3.7653809670640559</v>
       </c>
       <c r="K21" s="0">
-        <v>3.4234582414210162</v>
+        <v>4.9999992839498333</v>
       </c>
       <c r="L21" s="0">
-        <v>5.4769678638551742</v>
+        <v>14.99934712504303</v>
       </c>
       <c r="M21" s="0">
-        <v>4.9999999913622126</v>
+        <v>4.9999995130990875</v>
       </c>
       <c r="N21" s="0">
-        <v>0.85009860596547604</v>
+        <v>0.85002073702806624</v>
       </c>
       <c r="O21" s="0" t="s">
         <v>16</v>
@@ -1133,31 +1134,31 @@
         <v>0.59999999999999998</v>
       </c>
       <c r="F22" s="0">
-        <v>0.2088258831080686</v>
+        <v>0.10841212247053172</v>
       </c>
       <c r="G22" s="0">
-        <v>0.64382729654103876</v>
+        <v>0.56488378692249308</v>
       </c>
       <c r="H22" s="0">
-        <v>0.38212167014710441</v>
+        <v>0.77747542320596042</v>
       </c>
       <c r="I22" s="0">
-        <v>0.32542083460946136</v>
+        <v>0.57646540643566846</v>
       </c>
       <c r="J22" s="0">
-        <v>2.1175622144206479</v>
+        <v>3.61171585990264</v>
       </c>
       <c r="K22" s="0">
-        <v>4.936808731070677</v>
+        <v>4.999992306718017</v>
       </c>
       <c r="L22" s="0">
-        <v>6.4508207648433764</v>
+        <v>2.7335026603873076</v>
       </c>
       <c r="M22" s="0">
-        <v>4.9999985057985548</v>
+        <v>2.801955249234088</v>
       </c>
       <c r="N22" s="0">
-        <v>0.85032974273901174</v>
+        <v>0.85000729304896994</v>
       </c>
       <c r="O22" s="0" t="s">
         <v>16</v>
@@ -1180,31 +1181,31 @@
         <v>1.2</v>
       </c>
       <c r="F23" s="0">
-        <v>0.15438818817012995</v>
+        <v>0.0016489057529558912</v>
       </c>
       <c r="G23" s="0">
-        <v>0.037720158237347694</v>
+        <v>0.73745072804411271</v>
       </c>
       <c r="H23" s="0">
-        <v>0.11261372353509645</v>
+        <v>0.23444173289026368</v>
       </c>
       <c r="I23" s="0">
-        <v>0.74353342050982396</v>
+        <v>0.014784670767406995</v>
       </c>
       <c r="J23" s="0">
-        <v>2.3530938318043502</v>
+        <v>5.2731695799824427</v>
       </c>
       <c r="K23" s="0">
-        <v>4.9999998835886199</v>
+        <v>1.6417713363872986</v>
       </c>
       <c r="L23" s="0">
-        <v>0.30115605849112281</v>
+        <v>14.385666419784179</v>
       </c>
       <c r="M23" s="0">
-        <v>4.9999998547975801</v>
+        <v>3.355729091209211</v>
       </c>
       <c r="N23" s="0">
-        <v>0.85002606389632895</v>
+        <v>0.8615469494611494</v>
       </c>
       <c r="O23" s="0" t="s">
         <v>16</v>
@@ -1227,31 +1228,31 @@
         <v>1.8</v>
       </c>
       <c r="F24" s="0">
-        <v>0.23250732262289964</v>
+        <v>0.075657701403489333</v>
       </c>
       <c r="G24" s="0">
-        <v>0.23579759410292667</v>
+        <v>0.79998830573111768</v>
       </c>
       <c r="H24" s="0">
-        <v>0.73547775039621932</v>
+        <v>0.3428563091817049</v>
       </c>
       <c r="I24" s="0">
-        <v>0.47206367614680683</v>
+        <v>0.057933080704355433</v>
       </c>
       <c r="J24" s="0">
-        <v>2.076645149856712</v>
+        <v>4.5354920667695016</v>
       </c>
       <c r="K24" s="0">
-        <v>4.9995752401708575</v>
+        <v>4.2327294995907767</v>
       </c>
       <c r="L24" s="0">
-        <v>11.645483651650313</v>
+        <v>9.0445183240829064</v>
       </c>
       <c r="M24" s="0">
-        <v>2.5116287973071887</v>
+        <v>0.35137855052954992</v>
       </c>
       <c r="N24" s="0">
-        <v>0.85008860582859369</v>
+        <v>0.93288127280115685</v>
       </c>
       <c r="O24" s="0" t="s">
         <v>16</v>
@@ -1274,31 +1275,31 @@
         <v>2.3999999999999999</v>
       </c>
       <c r="F25" s="0">
-        <v>0.72259891807256316</v>
+        <v>0.33314141710300665</v>
       </c>
       <c r="G25" s="0">
-        <v>0.70022395261722337</v>
+        <v>0.13399756890158035</v>
       </c>
       <c r="H25" s="0">
-        <v>0.79749356507592528</v>
+        <v>0.43540330720643994</v>
       </c>
       <c r="I25" s="0">
-        <v>0.69257049833379447</v>
+        <v>0.41056111133168721</v>
       </c>
       <c r="J25" s="0">
-        <v>0.19823301075271371</v>
+        <v>5.4202308145656986</v>
       </c>
       <c r="K25" s="0">
-        <v>4.5309458589519611</v>
+        <v>2.7173463978056942</v>
       </c>
       <c r="L25" s="0">
-        <v>12.861964798910048</v>
+        <v>14.981167690405512</v>
       </c>
       <c r="M25" s="0">
-        <v>4.5833735845523886</v>
+        <v>4.9999998501232668</v>
       </c>
       <c r="N25" s="0">
-        <v>0.85023849057829937</v>
+        <v>0.85021359871716484</v>
       </c>
       <c r="O25" s="0" t="s">
         <v>16</v>
